--- a/nav_data/basic_infomation.xlsx
+++ b/nav_data/basic_infomation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17820\Desktop\Private_nav_research\nav_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1C0808-EF55-4804-B683-68CA3AC81CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4649DD68-41FD-41BC-8F29-6CD1D805199F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>fund_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,10 +98,6 @@
   </si>
   <si>
     <t>主观价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主观成长</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -491,7 +487,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
@@ -508,7 +504,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -525,7 +521,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>

--- a/nav_data/basic_infomation.xlsx
+++ b/nav_data/basic_infomation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17820\Desktop\Private_nav_research\nav_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4649DD68-41FD-41BC-8F29-6CD1D805199F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7C1492-0ECB-4CA6-9803-C453C532D686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/nav_data/basic_infomation.xlsx
+++ b/nav_data/basic_infomation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17820\Desktop\Private_nav_research\nav_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7C1492-0ECB-4CA6-9803-C453C532D686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08AB6AD-F26B-48E1-A6EF-D8A88F65F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,7 +445,7 @@
     <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
